--- a/Configs/GameConfig/Datas/fg/#BuildUpgrade-升级路线.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildUpgrade-升级路线.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,15 +576,33 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
+          <t>pipe_underground_t1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pipe_underground_t2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>地下管线 T1 → T2（FG4-ECO-10：已配对的一对一起升，差额 2 × 3 废料；跨度 8 → 12 只会变大，配对不变）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>power_pole</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>power_pole_t2</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>电塔 T1 → T2（差额 5 废料；覆盖半径 8 → 16）</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#BuildUpgrade-升级路线.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildUpgrade-升级路线.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,6 +608,42 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>barrier_t1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>barrier_t2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>屏障 T1 → T2（差额 3 废料；耐久 120 → 260）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>barrier_t2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>barrier_t3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>屏障 T2 → T3（差额 4 废料；耐久 260 → 480）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildUpgrade-升级路线.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildUpgrade-升级路线.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,17 +576,17 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pipe_underground_t1</t>
+          <t>pipe_t2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pipe_underground_t2</t>
+          <t>pipe_t3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>地下管线 T1 → T2（FG4-ECO-10：已配对的一对一起升，差额 2 × 3 废料；跨度 8 → 12 只会变大，配对不变）</t>
+          <t>管线 T2 → 伴热管（FG7-ENV-03：每格差额 1 废料；吞吐不变，寒潮不结冰）</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>power_pole</t>
+          <t>pipe_underground_t1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>power_pole_t2</t>
+          <t>pipe_underground_t2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>电塔 T1 → T2（差额 5 废料；覆盖半径 8 → 16）</t>
+          <t>地下管线 T1 → T2（FG4-ECO-10：已配对的一对一起升，差额 2 × 3 废料；跨度 8 → 12 只会变大，配对不变）</t>
         </is>
       </c>
     </row>
@@ -612,17 +612,17 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>barrier_t1</t>
+          <t>power_pole</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>barrier_t2</t>
+          <t>power_pole_t2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>屏障 T1 → T2（差额 3 废料；耐久 120 → 260）</t>
+          <t>电塔 T1 → T2（差额 5 废料；覆盖半径 8 → 16）</t>
         </is>
       </c>
     </row>
@@ -630,15 +630,33 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
+          <t>barrier_t1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>barrier_t2</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>屏障 T1 → T2（差额 3 废料；耐久 120 → 260）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>barrier_t2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>barrier_t3</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>屏障 T2 → T3（差额 4 废料；耐久 260 → 480）</t>
         </is>
